--- a/docs/产品图总览.xlsx
+++ b/docs/产品图总览.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品图总览" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品图总览'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品图总览'!$A$1:$H$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,11 +103,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,7 +120,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -133,7 +133,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,7 +221,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -246,7 +246,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -271,7 +271,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -296,7 +296,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -446,7 +446,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -471,7 +471,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -571,7 +571,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -646,7 +646,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -796,7 +796,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -821,7 +821,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -846,7 +846,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -896,7 +896,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -907,31 +907,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1234,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1293,56 +1268,52 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>四川辣酱（麦辣酱）</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>szechuan_sauce</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>szechuan_sauce.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>樱花麦旋风</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>sakura_mcfloat</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>sakura_mcfloat.jpg</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>官方海报·去水印抠图</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr"/>
     </row>
     <row r="3" ht="78" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="n"/>
+      <c r="B3" s="3" t="n"/>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>嫩牛五方</t>
+          <t>蒜蓉辣椒酱</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>nen_niu_wufang</t>
+          <t>garlic_chili_sauce</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>nen_niu_wufang.jpg</t>
+          <t>garlic_chili_sauce.jpg</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
@@ -1350,7 +1321,7 @@
           <t>网络搜集·已白底化</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -1361,36 +1332,40 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>墨西哥鸡肉卷</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>mexican_wrap</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>榴莲麦旋风（苏丹王榴莲）</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>durian_flavor</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>mexican_wrap.jpg</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
+          <t>durian_flavor.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1400,21 +1375,21 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>新奥尔良烤翅</t>
+          <t>五色蔬萃卷</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>neworleans_wing</t>
+          <t>five_color_veggie_roll</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>neworleans_wing.jpg（建议）</t>
+          <t>five_color_veggie_roll.jpg（建议）</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
@@ -1434,64 +1409,68 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>樱花麦旋风</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>sakura_mcfloat</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>sakura_mcfloat.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>五色嫩鸡麦饭卷</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>five_color_chicken_roll</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>five_color_chicken_roll.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>蒜蓉辣椒酱</t>
+          <t>五色至牛麦饭卷</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>garlic_chili_sauce</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>garlic_chili_sauce.jpg</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr"/>
+          <t>five_color_beef_roll</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>five_color_beef_roll.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="78" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1502,35 +1481,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>榴莲麦旋风（苏丹王榴莲）</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>durian_flavor</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>durian_flavor.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>五色开心卷</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>five_color_happy_roll</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>five_color_happy_roll.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1540,21 +1519,21 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>日食五色菠菜卷（2011 限定）</t>
+          <t>青柠味泰椒酱</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>five_color_burger</t>
+          <t>lime_thai_chili</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>five_color_burger.jpg（建议）</t>
+          <t>lime_thai_chili.jpg（建议）</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
@@ -1574,35 +1553,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>青柠味泰椒酱</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>lime_thai_chili</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>lime_thai_chili.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>新加坡蜜糖芥末酱</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>singapore_honey_mustard</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>singapore_honey_mustard.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1612,21 +1591,21 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>新加坡蜜糖芥末酱</t>
+          <t>法式芝士酱</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>singapore_honey_mustard</t>
+          <t>french_cheese</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>singapore_honey_mustard.jpg（建议）</t>
+          <t>french_cheese.jpg（建议）</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
@@ -1646,160 +1625,156 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>法式芝士酱</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>french_cheese</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>french_cheese.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>马来沙嗲酱</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>malay_satay</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>malay_satay.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
+      <c r="B13" s="3" t="n"/>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>马来沙嗲酱</t>
+          <t>麦饭卷</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>malay_satay</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>malay_satay.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>mc_rice_wrap</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>mc_rice_wrap.jpg</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="78" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>麦饭卷</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>mc_rice_wrap</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>麦趣饭</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>mc_rice_bowl</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>mc_rice_wrap.jpg</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
+          <t>mc_rice_bowl.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>摇摇薯条</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>shake_fries</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>shake_fries.png</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="78" customHeight="1">
-      <c r="A15" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>麦趣饭</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>mc_rice_bowl</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>mc_rice_bowl.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+      <c r="H15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="78" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>摇摇薯条</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>shake_fries</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>shake_fries.png</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>安格斯牛肉堡</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>angus_burger</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>angus_burger.jpg</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1807,34 +1782,34 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="n"/>
+      <c r="B17" s="3" t="n"/>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>安格斯牛肉堡</t>
+          <t>抹茶麦旋风</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>angus_burger</t>
+          <t>matcha_mcfloat</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>angus_burger.jpg</t>
+          <t>../v-mcflurry.png</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+          <t>设计稿插画</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -1845,25 +1820,25 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>抹茶麦旋风</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>matcha_mcfloat</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>../v-mcflurry.png</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>设计稿插画</t>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>香菜冰旋风</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>cilantro_mcfloat</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>cilantro_mcfloat.jpg</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1871,34 +1846,34 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="n"/>
+      <c r="B19" s="3" t="n"/>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>香菜冰旋风</t>
+          <t>紫薯派</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>cilantro_mcfloat</t>
+          <t>purple_sweet_potato_pie</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>cilantro_mcfloat.jpg</t>
+          <t>purple_sweet_potato_pie.gif</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -1909,23 +1884,23 @@
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>紫薯派</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>purple_sweet_potato_pie</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>purple_sweet_potato_pie.gif</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>香芋派</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>taro_pie</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>taro_pie.gif</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>官方菜单图</t>
         </is>
@@ -1935,39 +1910,43 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="n"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>香芋派</t>
+          <t>咸蛋黄鸡腿月饼</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>taro_pie</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>taro_pie.gif</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr"/>
+          <t>salted_egg_yolk_mooncake</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>salted_egg_yolk_mooncake.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="78" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -1978,158 +1957,154 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>咸蛋黄鸡腿月饼</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>salted_egg_yolk_mooncake</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>salted_egg_yolk_mooncake.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>小龙虾堡</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>crayfish_burger</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>crayfish_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="23" ht="78" customHeight="1">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>小龙虾堡</t>
+          <t>那么大鸡排</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>crayfish_burger</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>crayfish_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>big_chicken_steak</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>big_chicken_steak.png</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="78" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>那么大鸡排</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>big_chicken_steak</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>肉夹馍（金招牌）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>roujiamo</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>big_chicken_steak.png</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
+          <t>roujiamo.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>油条 + 豆浆</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>youtiao_doujiang</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>youtiao_doujiang.jpg</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>肉夹馍（金招牌）</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>roujiamo</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>roujiamo.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+      <c r="H25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="78" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>油条 + 豆浆</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>youtiao_doujiang</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>youtiao_doujiang.jpg</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>珍宝三角</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>treasure_triangle</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>treasure_triangle.jpg</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>网络搜集·已白底化</t>
         </is>
@@ -2139,26 +2114,26 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
     </row>
     <row r="27" ht="78" customHeight="1">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="n"/>
+      <c r="B27" s="3" t="n"/>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>珍宝三角</t>
+          <t>草莓奶昔</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>treasure_triangle</t>
+          <t>strawberry_milkshake</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>treasure_triangle.jpg</t>
+          <t>strawberry_milkshake.jpg</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -2166,7 +2141,7 @@
           <t>网络搜集·已白底化</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -2177,25 +2152,25 @@
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>草莓奶昔</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>strawberry_milkshake</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>strawberry_milkshake.jpg</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>扭扭薯条（双酱薯条）</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>twisty_fries</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>twisty_fries.png</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2203,102 +2178,102 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
     </row>
     <row r="29" ht="78" customHeight="1">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="n"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>扭扭薯条（双酱薯条）</t>
+          <t>热香饼</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>twisty_fries</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>twisty_fries.png</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr"/>
+          <t>hotcakes</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>hotcakes.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr"/>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="78" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>热香饼</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>hotcakes</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>hotcakes.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>苹果派</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>apple_pie</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>apple_pie.gif</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr"/>
     </row>
     <row r="31" ht="78" customHeight="1">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="n"/>
+      <c r="B31" s="3" t="n"/>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>苹果派</t>
+          <t>咔滋脆鸡堡</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>apple_pie</t>
+          <t>kakazu_crispy_chicken</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>apple_pie.gif</t>
+          <t>../v-crispy.png</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+          <t>设计稿插画</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -2309,25 +2284,25 @@
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>咔滋脆鸡堡</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>kakazu_crispy_chicken</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>../v-crispy.png</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>设计稿插画</t>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>麦乐酷</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>mccool</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>mccool.jpg</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2335,39 +2310,43 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
     </row>
     <row r="33" ht="78" customHeight="1">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>麦乐酷</t>
+          <t>菠萝虾堡</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>mccool</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>mccool.jpg</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr"/>
+          <t>pineapple_shrimp_burger</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>pineapple_shrimp_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr"/>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="78" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -2378,90 +2357,86 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>菠萝虾堡</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>pineapple_shrimp_burger</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>pineapple_shrimp_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>盐焗鸡翅</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>salt_baked_wing</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>salt_baked_wing.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="35" ht="78" customHeight="1">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
+      <c r="B35" s="3" t="n"/>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>盐焗鸡翅</t>
+          <t>美味鲜蔬杯</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>salt_baked_wing</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>salt_baked_wing.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>veggie_cup</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>veggie_cup.jpg</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="78" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>美味鲜蔬杯</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>veggie_cup</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>veggie_cup.jpg</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>奶昔</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>milkshake</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>milkshake.jpg</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>网络搜集·已白底化</t>
         </is>
@@ -2471,34 +2446,34 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr"/>
     </row>
     <row r="37" ht="78" customHeight="1">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="n"/>
+      <c r="B37" s="3" t="n"/>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>奶昔</t>
+          <t>薯条摇摇乐</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>milkshake</t>
+          <t>shake_fries_fun</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>milkshake.jpg</t>
+          <t>shake_fries_fun.png</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -2509,23 +2484,23 @@
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>薯条摇摇乐</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>shake_fries_fun</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>shake_fries_fun.png</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>蜜桃派</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>peach_pie</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>peach_pie.gif</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>官方菜单图</t>
         </is>
@@ -2535,26 +2510,26 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr"/>
     </row>
     <row r="39" ht="78" customHeight="1">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="n"/>
+      <c r="B39" s="3" t="n"/>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>蜜桃派</t>
+          <t>芒果派</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>peach_pie</t>
+          <t>mango_pie</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>peach_pie.gif</t>
+          <t>mango_pie.gif</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -2562,7 +2537,7 @@
           <t>官方菜单图</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -2573,23 +2548,23 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>芒果派</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>mango_pie</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>mango_pie.gif</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>奶黄派</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>custard_pie</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>custard_pie.gif</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>官方菜单图</t>
         </is>
@@ -2599,238 +2574,238 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr"/>
     </row>
     <row r="41" ht="78" customHeight="1">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="n"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>奶黄派</t>
+          <t>青花椒双堡</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>custard_pie</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>custard_pie.gif</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr"/>
+          <t>qinghuajiao_double</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>qinghuajiao_double.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr"/>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="78" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>青花椒双堡</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>qinghuajiao_double</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>qinghuajiao_double.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>卤辣板烧鸡腿堡</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>braised_spicy_burger</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>braised_spicy_burger.png</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr"/>
     </row>
     <row r="43" ht="78" customHeight="1">
-      <c r="A43" s="8" t="n">
+      <c r="A43" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="n"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>卤辣板烧鸡腿堡</t>
+          <t>芝香牛牛月亮堡</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>braised_spicy_burger</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>braised_spicy_burger.png</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr"/>
+          <t>cheese_beef_moon</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>cheese_beef_moon.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr"/>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="78" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>芝香牛牛月亮堡</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>cheese_beef_moon</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>cheese_beef_moon.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>V-CUT薯角</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>vcut_wedges</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>vcut_wedges.jpg</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr"/>
     </row>
     <row r="45" ht="78" customHeight="1">
-      <c r="A45" s="8" t="n">
+      <c r="A45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="9" t="n"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>V-CUT薯角</t>
+          <t>鳕鱼金砖</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>vcut_wedges</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>vcut_wedges.jpg</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr"/>
+          <t>cod_brick</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>cod_brick.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr"/>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="78" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>鳕鱼金砖</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>cod_brick</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>cod_brick.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>骨碌碌咖喱鸡翅</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>curry_wing</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>curry_wing.jpg</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr"/>
     </row>
     <row r="47" ht="78" customHeight="1">
-      <c r="A47" s="8" t="n">
+      <c r="A47" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="9" t="n"/>
+      <c r="B47" s="3" t="n"/>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>骨碌碌咖喱鸡翅</t>
+          <t>板烧鸡腿堡</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>curry_wing</t>
+          <t>grilled_chicken_burger</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>curry_wing.jpg</t>
+          <t>grilled_chicken_burger.png</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
@@ -2841,104 +2816,108 @@
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>板烧鸡腿堡</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>grilled_chicken_burger</t>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>香芋麦旋风</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>taro_mcfloat</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>grilled_chicken_burger.png</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
+          <t>taro_mcfloat.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="78" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>枫糖松饼汉堡</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>maple_pancake_burger</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>maple_pancake_burger.jpg</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49" ht="78" customHeight="1">
-      <c r="A49" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>香芋麦旋风</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>taro_mcfloat</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>taro_mcfloat.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="inlineStr"/>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+      <c r="H49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="78" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="9" t="n"/>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>枫糖松饼汉堡</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>maple_pancake_burger</t>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>热朱古力</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>hot_chocolate</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>maple_pancake_burger.jpg</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
+          <t>hot_chocolate.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="78" customHeight="1">
-      <c r="A51" s="8" t="n">
+      <c r="A51" s="9" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2948,21 +2927,21 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>热朱古力</t>
+          <t>泰式炭烤风味猪猪堡</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>hot_chocolate</t>
+          <t>thai_charcoal_pork_burger</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>hot_chocolate.jpg（建议）</t>
+          <t>thai_charcoal_pork_burger.jpg（建议）</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr"/>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
@@ -2982,35 +2961,1115 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>泰式炭烤风味猪猪堡</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>thai_charcoal_pork_burger</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>thai_charcoal_pork_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>麦辣鸡腿堡</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>spicy_chicken_burger</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>spicy_chicken_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="78" customHeight="1">
+      <c r="A53" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>巨无霸</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>big_mac</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>big_mac.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr"/>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="78" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>麦香鸡</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>mcchicken</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>mcchicken.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="78" customHeight="1">
+      <c r="A55" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>双层吉士堡</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>double_cheeseburger</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>double_cheeseburger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr"/>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="78" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>馒火的芝香猪排堡</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>mantou_pork_burger</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>mantou_pork_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="78" customHeight="1">
+      <c r="A57" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>有芝好虾堡</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>cheese_shrimp_burger_2015</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>cheese_shrimp_burger_2015.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr"/>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="78" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>年年有利堡</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>lucky_year_fish_burger</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>lucky_year_fish_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="78" customHeight="1">
+      <c r="A59" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>年年有福堡</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>lucky_year_fu_burger</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>lucky_year_fu_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr"/>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="78" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>爽辣柚香黑椒辣牛堡</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>yuzu_black_pepper_beef_burger</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>yuzu_black_pepper_beef_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="78" customHeight="1">
+      <c r="A61" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>红豆派</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>red_bean_pie</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>red_bean_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr"/>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="78" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>绿豆派</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>mung_bean_pie</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>mung_bean_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="78" customHeight="1">
+      <c r="A63" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>香蕉派</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>banana_pie</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>banana_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr"/>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="78" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>椰子派</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>coconut_pie</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>coconut_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="78" customHeight="1">
+      <c r="A65" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>玉米派</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>corn_pie</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>corn_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="78" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>巧克力派</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>chocolate_pie</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>chocolate_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="78" customHeight="1">
+      <c r="A67" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>香橙派</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>orange_pie</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>orange_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr"/>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="78" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>草莓派</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>strawberry_pie</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>strawberry_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="78" customHeight="1">
+      <c r="A69" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>红豆双皮奶派</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>red_bean_double_skin_pie</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>red_bean_double_skin_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="78" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>黑森林派</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>black_forest_pie</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>black_forest_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="78" customHeight="1">
+      <c r="A71" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>奇巧巧克力风味三角派</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>kitkat_triangle_pie</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>kitkat_triangle_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="78" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>抹茶豆乳派</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>matcha_dofu_pie</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>matcha_dofu_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="78" customHeight="1">
+      <c r="A73" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>抹茶黑蜜麻薯派</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>matcha_black_honey_mochi_pie</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>matcha_black_honey_mochi_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="78" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>苹果香蕉双拼迷你派</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>apple_banana_mini_pie</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>apple_banana_mini_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="78" customHeight="1">
+      <c r="A75" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>红豆年糕派</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>red_bean_rice_cake_pie</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>red_bean_rice_cake_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr"/>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="78" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>金拱门虾堡</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>golden_arches_shrimp_burger</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>golden_arches_shrimp_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="78" customHeight="1">
+      <c r="A77" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>金菠萝鸡扒麦满分</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>golden_pineapple_chicken_mcmuffin</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>golden_pineapple_chicken_mcmuffin.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr"/>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="78" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>芝士嘿凤梨板烧</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>cheese_pineapple_grilled_burger</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>cheese_pineapple_grilled_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="78" customHeight="1">
+      <c r="A79" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>叠叠卷</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>die_die_roll</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>die_die_roll.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr"/>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="78" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>洋葱乳酪摇摇薯条</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>onion_cheese_shake_fries</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>onion_cheese_shake_fries.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="78" customHeight="1">
+      <c r="A81" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>黄金洋葱圈</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>golden_onion_rings</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t>golden_onion_rings.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr"/>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="78" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>脆脆脆贡菜鸡肉卷</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>gongcai_chicken_wrap</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>gongcai_chicken_wrap.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H52"/>
+  <autoFilter ref="A1:H82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/docs/产品图总览.xlsx
+++ b/docs/产品图总览.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品图总览" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品图总览'!$A$1:$H$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品图总览'!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,12 +103,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,7 +123,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,10 +132,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -221,7 +221,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -246,7 +246,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -296,7 +296,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -321,7 +321,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -346,7 +346,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -371,7 +371,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -396,7 +396,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -421,7 +421,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -446,7 +446,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -521,7 +521,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -546,7 +546,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -571,7 +571,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -596,7 +596,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -621,7 +621,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -671,7 +671,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -696,7 +696,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -721,7 +721,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -746,7 +746,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -757,156 +757,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="857250" cy="857250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1209,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1268,65 +1118,73 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>樱花麦旋风</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>sakura_mcfloat</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>sakura_mcfloat.jpg</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>官方海报·去水印抠图</t>
-        </is>
-      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>sakura_mcfloat.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr"/>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="78" customHeight="1">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>蒜蓉辣椒酱</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>garlic_chili_sauce</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>garlic_chili_sauce.jpg</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr"/>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>garlic_chili_sauce.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="78" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -1337,35 +1195,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>榴莲麦旋风（苏丹王榴莲）</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>durian_flavor</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>durian_flavor.jpg（建议）</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1373,28 +1231,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>五色蔬萃卷</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>five_color_veggie_roll</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>five_color_veggie_roll.jpg（建议）</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -1409,35 +1267,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>五色嫩鸡麦饭卷</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>five_color_chicken_roll</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>five_color_chicken_roll.jpg（建议）</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1445,28 +1303,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>五色至牛麦饭卷</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>five_color_beef_roll</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>five_color_beef_roll.jpg（建议）</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -1481,35 +1339,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>五色开心卷</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>five_color_happy_roll</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>five_color_happy_roll.jpg（建议）</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1517,28 +1375,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>青柠味泰椒酱</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>lime_thai_chili</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>lime_thai_chili.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>蜂蜜芥末酱</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>singapore_honey_mustard</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>singapore_honey_mustard.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -1548,40 +1406,36 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>新加坡蜜糖芥末酱</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>singapore_honey_mustard</t>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>麦饭卷</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>mc_rice_wrap</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>singapore_honey_mustard.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
+          <t>mc_rice_wrap.jpg</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1589,28 +1443,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>法式芝士酱</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>french_cheese</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>french_cheese.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>麦趣饭</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>mc_rice_bowl</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>mc_rice_bowl.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -1620,225 +1474,225 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>马来沙嗲酱</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>malay_satay</t>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>摇摇薯条</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>shake_fries</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>malay_satay.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr"/>
+          <t>shake_fries.png</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="78" customHeight="1">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>麦饭卷</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>mc_rice_wrap</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>mc_rice_wrap.jpg</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>安格斯牛肉堡</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>angus_burger</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>angus_burger.jpg</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>网络搜集·已白底化</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
     </row>
     <row r="14" ht="78" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>麦趣饭</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>mc_rice_bowl</t>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>抹茶麦旋风</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>matcha_mcfloat</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>mc_rice_bowl.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
+          <t>../v-mcflurry.png</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>设计稿插画</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="78" customHeight="1">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>摇摇薯条</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>shake_fries</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>shake_fries.png</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>香菜冰旋风</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>cilantro_mcfloat</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>cilantro_mcfloat.png</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>用户实拍/替换素材</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="78" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>安格斯牛肉堡</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>angus_burger</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>angus_burger.jpg</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>香芋派</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>taro_pie</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>taro_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr"/>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>抹茶麦旋风</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>matcha_mcfloat</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>../v-mcflurry.png</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>设计稿插画</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>神鲜虾虾堡</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>crayfish_burger</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>crayfish_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="78" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>香菜冰旋风</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>cilantro_mcfloat</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>cilantro_mcfloat.jpg</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>那么大鸡排</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>big_chicken_steak</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>big_chicken_steak.png</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1846,63 +1700,67 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>紫薯派</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>purple_sweet_potato_pie</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>purple_sweet_potato_pie.gif</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>肉夹馍（金招牌）</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>roujiamo</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>roujiamo.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="78" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>香芋派</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>taro_pie</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>taro_pie.gif</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>油条 + 豆浆</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>youtiao_doujiang</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>youtiao_doujiang.jpg</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1910,201 +1768,193 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>咸蛋黄鸡腿月饼</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>salted_egg_yolk_mooncake</t>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>珍宝三角</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>treasure_triangle</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>salted_egg_yolk_mooncake.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>treasure_triangle.png</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>用户实拍/替换素材</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
     </row>
     <row r="22" ht="78" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>小龙虾堡</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>crayfish_burger</t>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>草莓奶昔</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>strawberry_milkshake</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>crayfish_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
+          <t>strawberry_milkshake.jpg</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="78" customHeight="1">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>那么大鸡排</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>big_chicken_steak</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>big_chicken_steak.png</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>热香饼</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>hotcakes</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>hotcakes.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="78" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>肉夹馍（金招牌）</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>roujiamo</t>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>苹果派</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>apple_pie</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>roujiamo.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
+          <t>apple_pie.gif</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
     </row>
     <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>油条 + 豆浆</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>youtiao_doujiang</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>youtiao_doujiang.jpg</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>咔滋脆鸡堡</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>kakazu_crispy_chicken</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>../v-crispy.png</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>设计稿插画</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
     </row>
     <row r="26" ht="78" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>珍宝三角</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>treasure_triangle</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>treasure_triangle.jpg</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>麦乐酷</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>mccool</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>mccool.jpg</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>网络搜集·已白底化</t>
         </is>
@@ -2114,195 +1964,199 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
     </row>
     <row r="27" ht="78" customHeight="1">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>草莓奶昔</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>strawberry_milkshake</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>strawberry_milkshake.jpg</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>菠萝虾堡</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>pineapple_shrimp_burger</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>pineapple_shrimp_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="78" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>扭扭薯条（双酱薯条）</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>twisty_fries</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>twisty_fries.png</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>盐焗鸡翅</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>salt_baked_wing</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>salt_baked_wing.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>美味鲜蔬杯</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>veggie_cup</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>veggie_cup.jpg</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="78" customHeight="1">
-      <c r="A29" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>热香饼</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>hotcakes</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>hotcakes.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr"/>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+      <c r="H29" s="13" t="inlineStr"/>
     </row>
     <row r="30" ht="78" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>苹果派</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>apple_pie</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>apple_pie.gif</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>奶昔</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>milkshake</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>milkshake.jpg</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="78" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>蜜桃派</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>peach_pie</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>peach_pie.gif</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>官方菜单图</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31" ht="78" customHeight="1">
-      <c r="A31" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>咔滋脆鸡堡</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>kakazu_crispy_chicken</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>../v-crispy.png</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>设计稿插画</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr"/>
     </row>
     <row r="32" ht="78" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>麦乐酷</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>mccool</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>mccool.jpg</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>芒果派</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>mango_pie</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>mango_pie.gif</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2310,43 +2164,39 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
     </row>
     <row r="33" ht="78" customHeight="1">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>🥫</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>菠萝虾堡</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>pineapple_shrimp_burger</t>
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>奶黄派</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>custard_pie</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>pineapple_shrimp_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr"/>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
-        </is>
-      </c>
+          <t>custard_pie.gif</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>✅ 有图</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr"/>
     </row>
     <row r="34" ht="78" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -2357,214 +2207,222 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>盐焗鸡翅</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>salt_baked_wing</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>salt_baked_wing.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>青花椒双堡</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>qinghuajiao_double</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>qinghuajiao_double.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="35" ht="78" customHeight="1">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>美味鲜蔬杯</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>veggie_cup</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>veggie_cup.jpg</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>卤辣板烧鸡腿堡</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>braised_spicy_burger</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>braised_spicy_burger.png</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>官方菜单图</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr"/>
     </row>
     <row r="36" ht="78" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>奶昔</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>milkshake</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>milkshake.jpg</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>芝香牛牛月亮堡</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>cheese_beef_moon</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>cheese_beef_moon.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="78" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>V-CUT薯角</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>vcut_wedges</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>vcut_wedges.jpg</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>网络搜集·已白底化</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37" ht="78" customHeight="1">
-      <c r="A37" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>薯条摇摇乐</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>shake_fries_fun</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>shake_fries_fun.png</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr"/>
+      <c r="H37" s="13" t="inlineStr"/>
     </row>
     <row r="38" ht="78" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>蜜桃派</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>peach_pie</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>peach_pie.gif</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>鳕鱼金砖</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>cod_brick</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>cod_brick.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="78" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>骨碌碌咖喱鸡翅</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>curry_wing</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>curry_wing.jpg</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39" ht="78" customHeight="1">
-      <c r="A39" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>芒果派</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>mango_pie</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>mango_pie.gif</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr"/>
     </row>
     <row r="40" ht="78" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>奶黄派</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>custard_pie</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>custard_pie.gif</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>板烧鸡腿堡</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>grilled_chicken_burger</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>grilled_chicken_burger.png</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>官方菜单图</t>
         </is>
@@ -2574,10 +2432,10 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
     </row>
     <row r="41" ht="78" customHeight="1">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2585,28 +2443,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>青花椒双堡</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>qinghuajiao_double</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>qinghuajiao_double.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr"/>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>香芋麦旋风</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>taro_mcfloat</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>taro_mcfloat.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -2616,25 +2474,25 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>卤辣板烧鸡腿堡</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>braised_spicy_burger</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>braised_spicy_burger.png</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>枫糖松饼汉堡</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>maple_pancake_burger</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>maple_pancake_burger.jpg</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>网络搜集·已白底化</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2642,10 +2500,10 @@
           <t>✅ 有图</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
     </row>
     <row r="43" ht="78" customHeight="1">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="8" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2653,28 +2511,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>芝香牛牛月亮堡</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>cheese_beef_moon</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>cheese_beef_moon.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr"/>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>热朱古力</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>hot_chocolate</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>hot_chocolate.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -2684,36 +2542,40 @@
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>V-CUT薯角</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>vcut_wedges</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>vcut_wedges.jpg</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>泰式炭烤风味猪猪堡</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>thai_charcoal_pork_burger</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>thai_charcoal_pork_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr"/>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="78" customHeight="1">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2721,28 +2583,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>鳕鱼金砖</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>cod_brick</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>cod_brick.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="inlineStr"/>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>麦辣鸡腿堡</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>spicy_chicken_burger</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>spicy_chicken_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -2752,65 +2614,73 @@
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>骨碌碌咖喱鸡翅</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>curry_wing</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>curry_wing.jpg</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>巨无霸</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>big_mac</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>big_mac.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr"/>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="78" customHeight="1">
-      <c r="A47" s="9" t="n">
+      <c r="A47" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>板烧鸡腿堡</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>grilled_chicken_burger</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>grilled_chicken_burger.png</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="inlineStr">
-        <is>
-          <t>官方菜单图</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>麦香鸡</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>mcchicken</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>mcchicken.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="78" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -2821,64 +2691,68 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>香芋麦旋风</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>taro_mcfloat</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>taro_mcfloat.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>双层吉士堡</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>double_cheeseburger</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>double_cheeseburger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="49" ht="78" customHeight="1">
-      <c r="A49" s="9" t="n">
+      <c r="A49" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>枫糖松饼汉堡</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>maple_pancake_burger</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>maple_pancake_burger.jpg</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>网络搜集·已白底化</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>✅ 有图</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>馒火的芝香猪排堡</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>mantou_pork_burger</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>mantou_pork_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="78" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -2889,35 +2763,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>热朱古力</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>hot_chocolate</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>hot_chocolate.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>有芝好虾堡</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>cheese_shrimp_burger_2015</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>cheese_shrimp_burger_2015.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="51" ht="78" customHeight="1">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="8" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2925,28 +2799,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>泰式炭烤风味猪猪堡</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>thai_charcoal_pork_burger</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>thai_charcoal_pork_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F51" s="13" t="inlineStr"/>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>年年有利堡</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>lucky_year_fish_burger</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>lucky_year_fish_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -2961,35 +2835,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>麦辣鸡腿堡</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>spicy_chicken_burger</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>spicy_chicken_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>年年有福堡</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>lucky_year_fu_burger</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>lucky_year_fu_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="53" ht="78" customHeight="1">
-      <c r="A53" s="9" t="n">
+      <c r="A53" s="8" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2997,28 +2871,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>巨无霸</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>big_mac</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>big_mac.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="inlineStr"/>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>爽辣柚香黑椒辣牛堡</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>yuzu_black_pepper_beef_burger</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>yuzu_black_pepper_beef_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3033,35 +2907,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>麦香鸡</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>mcchicken</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>mcchicken.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>红豆派</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>red_bean_pie</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>red_bean_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="55" ht="78" customHeight="1">
-      <c r="A55" s="9" t="n">
+      <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3069,28 +2943,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>双层吉士堡</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>double_cheeseburger</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>double_cheeseburger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="inlineStr"/>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>绿豆派</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>mung_bean_pie</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>mung_bean_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr"/>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3105,35 +2979,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>馒火的芝香猪排堡</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>mantou_pork_burger</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>mantou_pork_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>香蕉派</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>banana_pie</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>banana_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="57" ht="78" customHeight="1">
-      <c r="A57" s="9" t="n">
+      <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3141,28 +3015,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>有芝好虾堡</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>cheese_shrimp_burger_2015</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>cheese_shrimp_burger_2015.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F57" s="13" t="inlineStr"/>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>椰子派</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>coconut_pie</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>coconut_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr"/>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3177,35 +3051,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>年年有利堡</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>lucky_year_fish_burger</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>lucky_year_fish_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>玉米派</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>corn_pie</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>corn_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="59" ht="78" customHeight="1">
-      <c r="A59" s="9" t="n">
+      <c r="A59" s="8" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3213,28 +3087,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>年年有福堡</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>lucky_year_fu_burger</t>
-        </is>
-      </c>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>lucky_year_fu_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="inlineStr"/>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H59" s="14" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>巧克力派</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>chocolate_pie</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>chocolate_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3249,35 +3123,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>爽辣柚香黑椒辣牛堡</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>yuzu_black_pepper_beef_burger</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>yuzu_black_pepper_beef_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>香橙派</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>orange_pie</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>orange_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="61" ht="78" customHeight="1">
-      <c r="A61" s="9" t="n">
+      <c r="A61" s="8" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3285,28 +3159,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>红豆派</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>red_bean_pie</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>red_bean_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="inlineStr"/>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H61" s="14" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>草莓派</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>strawberry_pie</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>strawberry_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3321,35 +3195,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>绿豆派</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>mung_bean_pie</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>mung_bean_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>红豆双皮奶派</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>red_bean_double_skin_pie</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>red_bean_double_skin_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="63" ht="78" customHeight="1">
-      <c r="A63" s="9" t="n">
+      <c r="A63" s="8" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3357,28 +3231,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>香蕉派</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>banana_pie</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>banana_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="inlineStr"/>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H63" s="14" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>黑森林派</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>black_forest_pie</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>black_forest_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3393,35 +3267,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>椰子派</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>coconut_pie</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>coconut_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>奇巧巧克力风味三角派</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>kitkat_triangle_pie</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>kitkat_triangle_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="65" ht="78" customHeight="1">
-      <c r="A65" s="9" t="n">
+      <c r="A65" s="8" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3429,28 +3303,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>玉米派</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>corn_pie</t>
-        </is>
-      </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>corn_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="inlineStr"/>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>抹茶豆乳派</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>matcha_dofu_pie</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>matcha_dofu_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr"/>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3465,35 +3339,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>巧克力派</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>chocolate_pie</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>chocolate_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>抹茶黑蜜麻薯派</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>matcha_black_honey_mochi_pie</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>matcha_black_honey_mochi_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="67" ht="78" customHeight="1">
-      <c r="A67" s="9" t="n">
+      <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3501,28 +3375,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>香橙派</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>orange_pie</t>
-        </is>
-      </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>orange_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="inlineStr"/>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H67" s="14" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>苹果香蕉双拼迷你派</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>apple_banana_mini_pie</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>apple_banana_mini_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3537,35 +3411,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>草莓派</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>strawberry_pie</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>strawberry_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>红豆年糕派</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>red_bean_rice_cake_pie</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>red_bean_rice_cake_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="69" ht="78" customHeight="1">
-      <c r="A69" s="9" t="n">
+      <c r="A69" s="8" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3573,28 +3447,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>红豆双皮奶派</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>red_bean_double_skin_pie</t>
-        </is>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>red_bean_double_skin_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="inlineStr"/>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H69" s="14" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>金拱门虾堡</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>golden_arches_shrimp_burger</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>golden_arches_shrimp_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3609,35 +3483,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>黑森林派</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>black_forest_pie</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
-        <is>
-          <t>black_forest_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>金菠萝鸡扒麦满分</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>golden_pineapple_chicken_mcmuffin</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>golden_pineapple_chicken_mcmuffin.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="71" ht="78" customHeight="1">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="8" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3645,28 +3519,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>奇巧巧克力风味三角派</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>kitkat_triangle_pie</t>
-        </is>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>kitkat_triangle_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="inlineStr"/>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H71" s="14" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>芝士嘿凤梨板烧</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>cheese_pineapple_grilled_burger</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>cheese_pineapple_grilled_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3681,35 +3555,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>抹茶豆乳派</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>matcha_dofu_pie</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>matcha_dofu_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>叠叠卷</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>die_die_roll</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>die_die_roll.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="73" ht="78" customHeight="1">
-      <c r="A73" s="9" t="n">
+      <c r="A73" s="8" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3717,28 +3591,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>抹茶黑蜜麻薯派</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>matcha_black_honey_mochi_pie</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="inlineStr">
-        <is>
-          <t>matcha_black_honey_mochi_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F73" s="13" t="inlineStr"/>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H73" s="14" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>洋葱乳酪摇摇薯条</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>onion_cheese_shake_fries</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>onion_cheese_shake_fries.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3753,35 +3627,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>苹果香蕉双拼迷你派</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>apple_banana_mini_pie</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="inlineStr">
-        <is>
-          <t>apple_banana_mini_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>黄金洋葱圈</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>golden_onion_rings</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>golden_onion_rings.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H74" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="75" ht="78" customHeight="1">
-      <c r="A75" s="9" t="n">
+      <c r="A75" s="8" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3789,28 +3663,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>红豆年糕派</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>red_bean_rice_cake_pie</t>
-        </is>
-      </c>
-      <c r="E75" s="16" t="inlineStr">
-        <is>
-          <t>red_bean_rice_cake_pie.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F75" s="13" t="inlineStr"/>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H75" s="14" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>脆脆脆贡菜鸡肉卷</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>gongcai_chicken_wrap</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>gongcai_chicken_wrap.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr"/>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H75" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3825,35 +3699,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>金拱门虾堡</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>golden_arches_shrimp_burger</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>golden_arches_shrimp_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>奇妙泰椒酱</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>thai_chili_mayo</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>thai_chili_mayo.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="77" ht="78" customHeight="1">
-      <c r="A77" s="9" t="n">
+      <c r="A77" s="8" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3861,28 +3735,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>金菠萝鸡扒麦满分</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>golden_pineapple_chicken_mcmuffin</t>
-        </is>
-      </c>
-      <c r="E77" s="16" t="inlineStr">
-        <is>
-          <t>golden_pineapple_chicken_mcmuffin.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F77" s="13" t="inlineStr"/>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H77" s="14" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>中式咕噜酱</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>gulu_sauce</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>gulu_sauce.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3897,35 +3771,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>芝士嘿凤梨板烧</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>cheese_pineapple_grilled_burger</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr">
-        <is>
-          <t>cheese_pineapple_grilled_burger.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>咸蛋黄鸡腿蛋月堡</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>salted_egg_yolk_moon_burger</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>salted_egg_yolk_moon_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="79" ht="78" customHeight="1">
-      <c r="A79" s="9" t="n">
+      <c r="A79" s="8" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3933,28 +3807,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>叠叠卷</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>die_die_roll</t>
-        </is>
-      </c>
-      <c r="E79" s="16" t="inlineStr">
-        <is>
-          <t>die_die_roll.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr"/>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H79" s="14" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>油泼辣子新地</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>youpo_lazi_sundae</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>youpo_lazi_sundae.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -3969,35 +3843,35 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>洋葱乳酪摇摇薯条</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>onion_cheese_shake_fries</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>onion_cheese_shake_fries.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>脏脏年糕麦旋风</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>dirty_rice_cake_mcfloat</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>dirty_rice_cake_mcfloat.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H80" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
     <row r="81" ht="78" customHeight="1">
-      <c r="A81" s="9" t="n">
+      <c r="A81" s="8" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4005,28 +3879,28 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>黄金洋葱圈</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>golden_onion_rings</t>
-        </is>
-      </c>
-      <c r="E81" s="16" t="inlineStr">
-        <is>
-          <t>golden_onion_rings.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H81" s="14" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>大盘鸡辣堡</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>dapanji_spicy_burger</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>dapanji_spicy_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
@@ -4041,35 +3915,611 @@
           <t>🥫</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>脆脆脆贡菜鸡肉卷</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>gongcai_chicken_wrap</t>
-        </is>
-      </c>
-      <c r="E82" s="15" t="inlineStr">
-        <is>
-          <t>gongcai_chicken_wrap.jpg（建议）</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>葡萄酸奶燕麦麦旋风</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>grape_yogurt_oat_mcfloat</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>grape_yogurt_oat_mcfloat.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="78" customHeight="1">
+      <c r="A83" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>火腿蛋麦香酥</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>ham_egg_mc_crisp</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>ham_egg_mc_crisp.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="78" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>爆浆芝士鸡排堡</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>cheese_burst_chicken_patty_burger</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>cheese_burst_chicken_patty_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="78" customHeight="1">
+      <c r="A85" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>金球堡</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>golden_ball_burger</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>golden_ball_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="78" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>脆皮枫糖风味鸡翅</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>maple_glazed_chicken_wings</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>maple_glazed_chicken_wings.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="78" customHeight="1">
+      <c r="A87" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>玉兔望月</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>jade_rabbit_moon</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>jade_rabbit_moon.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="78" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>鸳鸯奶茶冰淇淋</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>yuanyang_milk_tea_icecream</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>yuanyang_milk_tea_icecream.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="78" customHeight="1">
+      <c r="A89" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>樱花口味冰淇淋</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>sakura_icecream</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>sakura_icecream.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="78" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>草莓甜筒</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>strawberry_cone</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>strawberry_cone.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="78" customHeight="1">
+      <c r="A91" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>那么大系列甜筒</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>danala_cone_series</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>danala_cone_series.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="78" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>红提冰淇淋</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>red_grape_icecream</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>red_grape_icecream.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="78" customHeight="1">
+      <c r="A93" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>芝士冰淇淋</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>cheese_icecream</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>cheese_icecream.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr"/>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="78" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>黑芝麻冰淇淋</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>black_sesame_icecream</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>black_sesame_icecream.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="78" customHeight="1">
+      <c r="A95" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>田园派</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>tianyuan_pie</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>tianyuan_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="78" customHeight="1">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>热派</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>hot_pie</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>hot_pie.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="78" customHeight="1">
+      <c r="A97" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>扭扭薯条</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>twisted_fries</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>twisted_fries.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="78" customHeight="1">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>🥫</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>腊味菜菜堡</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>wax_cabbage_burger</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>wax_cabbage_burger.jpg（建议）</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>❌ 缺失</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>找到图片后按本行「图片文件名」列的建议名放入 web/assets/products/，即可接入页面</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H82"/>
+  <autoFilter ref="A1:H98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
